--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_PONSOL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε.(181)_2026-02.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_PONSOL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε.(181)_2026-02.xlsx
@@ -2845,7 +2845,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>06/03/26</t>
+          <t>09/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3197,13 +3197,13 @@
         <v>1299.16</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0</v>
+        <v>33.1560312</v>
       </c>
       <c r="F23" s="25" t="n">
         <v>1.3</v>
       </c>
       <c r="G23" s="92" t="n">
-        <v>0</v>
+        <v>25.52</v>
       </c>
       <c r="H23" s="93" t="n"/>
     </row>
@@ -3237,13 +3237,13 @@
         <v>2242.68</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>0</v>
+        <v>20.6030716</v>
       </c>
       <c r="F25" s="25" t="n">
         <v>2.24</v>
       </c>
       <c r="G25" s="92" t="n">
-        <v>0</v>
+        <v>9.19</v>
       </c>
       <c r="H25" s="93" t="n"/>
     </row>
@@ -3417,13 +3417,13 @@
         <v>3210.44</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>0</v>
+        <v>13.3713174</v>
       </c>
       <c r="F34" s="25" t="n">
         <v>3.21</v>
       </c>
       <c r="G34" s="92" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="H34" s="93" t="n"/>
     </row>
@@ -3437,13 +3437,13 @@
         <v>3127.38</v>
       </c>
       <c r="E35" s="25" t="n">
-        <v>16.9598938</v>
+        <v>13.7430268</v>
       </c>
       <c r="F35" s="25" t="n">
         <v>3.13</v>
       </c>
       <c r="G35" s="92" t="n">
-        <v>5.42</v>
+        <v>4.39</v>
       </c>
       <c r="H35" s="93" t="n"/>
     </row>
@@ -3457,13 +3457,13 @@
         <v>3134.46</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>0</v>
+        <v>47.895081</v>
       </c>
       <c r="F36" s="25" t="n">
         <v>3.13</v>
       </c>
       <c r="G36" s="92" t="n">
-        <v>0</v>
+        <v>15.28</v>
       </c>
       <c r="H36" s="93" t="n"/>
     </row>
@@ -3477,13 +3477,13 @@
         <v>2066.96</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>0</v>
+        <v>6.0563912</v>
       </c>
       <c r="F37" s="25" t="n">
         <v>2.07</v>
       </c>
       <c r="G37" s="92" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="H37" s="93" t="n"/>
     </row>
@@ -3497,13 +3497,13 @@
         <v>47677.16</v>
       </c>
       <c r="E38" s="95" t="n">
-        <v>1215.68</v>
+        <v>1333.54</v>
       </c>
       <c r="F38" s="95" t="n">
         <v>47.68</v>
       </c>
       <c r="G38" s="96" t="n">
-        <v>25.5</v>
+        <v>27.97</v>
       </c>
       <c r="H38" s="93" t="n"/>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G46" s="83" t="n"/>
       <c r="H46" s="105" t="n">
-        <v>1215.68</v>
+        <v>1333.54</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="C53" s="110" t="inlineStr">
         <is>
-          <t>08/03/26</t>
+          <t>11/03/26</t>
         </is>
       </c>
       <c r="D53" s="111" t="n"/>
